--- a/artfynd/A 31431-2024 artfynd.xlsx
+++ b/artfynd/A 31431-2024 artfynd.xlsx
@@ -1311,7 +1311,7 @@
         <v>119758032</v>
       </c>
       <c r="B7" t="n">
-        <v>105090</v>
+        <v>105113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 31431-2024 artfynd.xlsx
+++ b/artfynd/A 31431-2024 artfynd.xlsx
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>

--- a/artfynd/A 31431-2024 artfynd.xlsx
+++ b/artfynd/A 31431-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3784085</v>
+        <v>640827</v>
       </c>
       <c r="B2" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>2604</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593833.7537310836</v>
+        <v>593861</v>
       </c>
       <c r="R2" t="n">
-        <v>6398975.610768905</v>
+        <v>6398970</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,14 @@
           <t>2006-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-10-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>måttligt på några block</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +764,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>blockig ekskog</t>
+          <t>blockig ädellövskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>på block nedan grov tidigare hamlad lind</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>640827</v>
+        <v>701814</v>
       </c>
       <c r="B3" t="n">
-        <v>95245</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593860.6523999551</v>
+        <v>593824</v>
       </c>
       <c r="R3" t="n">
-        <v>6398969.825270076</v>
+        <v>6398975</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +855,14 @@
           <t>2006-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-10-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>måttligt på några block</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +876,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>blockig ädellövskog</t>
+          <t>blockig ekskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>på block nedan grov tidigare hamlad lind</t>
+          <t>stenblock</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>701814</v>
+        <v>724599</v>
       </c>
       <c r="B4" t="n">
-        <v>93131</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593823.5888712623</v>
+        <v>593869</v>
       </c>
       <c r="R4" t="n">
-        <v>6398975.374416535</v>
+        <v>6398972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,24 +967,14 @@
           <t>2006-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2006-10-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>rikligt på 2 träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,12 +988,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>blockig ekskog</t>
+          <t>blockig ädellövskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>stenblock</t>
+          <t>grov tidigare hamlad lind</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13223614</v>
+        <v>102801090</v>
       </c>
       <c r="B5" t="n">
-        <v>9259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,39 +1022,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101254</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skeppsvarvsfluga</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lymexylon navale</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Värkebäcksviken, Sm</t>
+          <t>Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593994.6730269628</v>
+        <v>593968</v>
       </c>
       <c r="R5" t="n">
-        <v>6398800.376220548</v>
+        <v>6398798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,29 +1078,19 @@
           <t>Gladhammar</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>668E3597-61BC-41A2-B6B2-5C9E4BB424B0</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2006-10-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2006-10-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 träd troligen pågående angrepp</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,35 +1102,39 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>ekhage mot granskog, 90 cm ek</t>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Thomas Johansson, Julia Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102801156</v>
+        <v>102801155</v>
       </c>
       <c r="B6" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593824.8078390616</v>
+        <v>593885</v>
       </c>
       <c r="R6" t="n">
-        <v>6398968.991692593</v>
+        <v>6398923</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,7 +1200,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>9CBD396F-EE14-4D88-86DF-EC69437E78C5</t>
+          <t>DE3DCCF8-9FE6-4054-A261-42A76B6FDCFB</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1255,26 +1208,16 @@
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1308,65 +1251,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119758032</v>
+        <v>102801156</v>
       </c>
       <c r="B7" t="n">
-        <v>105113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221423</v>
+        <v>5445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kläcksvik, Sm</t>
+          <t>Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593839</v>
+        <v>593825</v>
       </c>
       <c r="R7" t="n">
-        <v>6398942</v>
+        <v>6398969</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,40 +1318,1183 @@
           <t>Gladhammar</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>9CBD396F-EE14-4D88-86DF-EC69437E78C5</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Petter Almgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1859053</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Värkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593759</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6398987</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rikligt på 2 träd</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>ekhage mot sjö</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>grova hagmarksekar</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2379687</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Värkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>593965</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398844</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sparsamt på 1 träd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>ekskog nedan sydvänd brant</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grovbarkig 1m bred ek</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13223627</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9363</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101254</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skeppsvarvsfluga</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lymexylon navale</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Värkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593752</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398979</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 träd</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>ekhage mot sjö, blixtärr i grov hagmarksek</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3784085</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Värkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>593834</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398976</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>blockig ekskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119758032</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kläcksvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>593839</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398942</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Larsgunnar Nilsson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>102801091</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalmar län, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>594005</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6398848</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>DBEE59BB-22CD-4254-BB72-C724795D2C19</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Julia Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>102801092</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalmar län, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>594014</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6398862</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>30A0A1E6-FCB0-4825-8153-119A56D0906D</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Thomas Johansson, Julia Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13223614</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9363</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101254</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skeppsvarvsfluga</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lymexylon navale</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Värkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>593995</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398800</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 träd troligen pågående angrepp</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>ekhage mot granskog, 90 cm ek</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13223625</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9363</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101254</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skeppsvarvsfluga</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lymexylon navale</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Värkebäcksviken, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>594009</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398849</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2006-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>avslutat gnag i 1 träd</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>sydvänd ädellövskog , stamskada i grov ek</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>99394474</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalmar län, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>594021</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6398856</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>17181ED7-4AE2-4686-A952-28E2D356A4C7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mätt 50cm från marknivå.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
         </is>
       </c>
     </row>
